--- a/Attendance Roster_Splunk Intermediate_April 06-08_APJC.xlsx
+++ b/Attendance Roster_Splunk Intermediate_April 06-08_APJC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_INDIA_06_04_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8AB91D-63F6-4914-AC31-22DCE637C434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64ED29A0-BF0B-4434-A71A-182430AB4AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{12C6C05F-C4ED-4B83-AFD1-0B63BF77D5C5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12C6C05F-C4ED-4B83-AFD1-0B63BF77D5C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="48">
   <si>
     <t>Start Date</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>https://cloud.cdp.rpsconsulting.in/console/#</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -663,21 +666,21 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1025,10 +1028,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="32"/>
+      <c r="C1" s="36"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1125,7 +1128,9 @@
       <c r="B12" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12"/>
+      <c r="C12" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="D12" s="12"/>
       <c r="E12" s="13"/>
     </row>
@@ -1136,7 +1141,9 @@
       <c r="B13" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="7"/>
     </row>
@@ -1147,7 +1154,9 @@
       <c r="B14" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="7"/>
     </row>
@@ -1158,7 +1167,9 @@
       <c r="B15" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D15" s="5"/>
       <c r="E15" s="7"/>
     </row>
@@ -1169,7 +1180,9 @@
       <c r="B16" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D16" s="5"/>
       <c r="E16" s="7"/>
     </row>
@@ -1180,7 +1193,9 @@
       <c r="B17" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="5"/>
+      <c r="C17" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D17" s="5"/>
       <c r="E17" s="7"/>
     </row>
@@ -1191,7 +1206,9 @@
       <c r="B18" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D18" s="5"/>
       <c r="E18" s="7"/>
     </row>
@@ -1202,7 +1219,9 @@
       <c r="B19" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D19" s="5"/>
       <c r="E19" s="7"/>
     </row>
@@ -1211,7 +1230,9 @@
         <v>30</v>
       </c>
       <c r="B20" s="23"/>
-      <c r="C20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D20" s="6"/>
       <c r="E20" s="8"/>
     </row>
@@ -1222,7 +1243,9 @@
       <c r="B21" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D21" s="6"/>
       <c r="E21" s="8"/>
     </row>
@@ -1233,7 +1256,9 @@
       <c r="B22" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="5"/>
+      <c r="C22" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="D22" s="6"/>
       <c r="E22" s="8"/>
     </row>
@@ -1244,7 +1269,9 @@
       <c r="B23" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
     </row>
@@ -1272,214 +1299,214 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="31" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="32" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="32" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="32" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="32" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="32" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="32" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="32" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="32" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="23"/>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="32" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="32" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="33" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="33" t="s">
         <v>32</v>
       </c>
     </row>

--- a/Attendance Roster_Splunk Intermediate_April 06-08_APJC.xlsx
+++ b/Attendance Roster_Splunk Intermediate_April 06-08_APJC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_INDIA_06_04_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64ED29A0-BF0B-4434-A71A-182430AB4AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43E583C-4105-46EF-B053-CDDA05D8CF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12C6C05F-C4ED-4B83-AFD1-0B63BF77D5C5}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="48">
   <si>
     <t>Start Date</t>
   </si>
@@ -287,7 +287,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -408,173 +408,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -584,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -600,27 +441,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -636,7 +456,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -645,27 +465,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -673,14 +472,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="15" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1028,10 +830,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="36"/>
+      <c r="C1" s="19"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1042,40 +844,40 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="12">
         <v>46118</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="13">
         <v>46120</v>
       </c>
       <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="7">
         <v>12</v>
       </c>
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="4"/>
@@ -1098,182 +900,206 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="21">
         <v>46118</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="21">
         <v>46119</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="21">
         <v>46120</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
+      <c r="C12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="7"/>
+      <c r="D13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="7"/>
+      <c r="D14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="14" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="7"/>
+      <c r="D15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="7"/>
+      <c r="D16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="7"/>
+      <c r="D17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="7"/>
+      <c r="D18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="7"/>
+      <c r="D19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="23"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="8"/>
+      <c r="D20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="8"/>
+      <c r="D21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="8"/>
-    </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="29" t="s">
+      <c r="D22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="11"/>
+      <c r="C23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1299,214 +1125,214 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="33" t="s">
+      <c r="C17" s="14"/>
+      <c r="D17" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E18" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E19" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E20" s="17" t="s">
         <v>32</v>
       </c>
     </row>
